--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q150"/>
+  <dimension ref="A1:Q200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8754,6 +8754,1952 @@
         </is>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>University of Cambridge</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>https://www.cam.ac.uk</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Imperial College London</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>https://www.imperial.ac.uk</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>University of Chinese Academy of Sciences</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>https://www.ucas.ac.cn</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>The University of Osaka</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>https://www.osaka-u.ac.jp</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>University of Manchester</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>https://www.manchester.ac.uk/</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr"/>
+      <c r="P155" t="inlineStr"/>
+      <c r="Q155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Sapienza University of Rome</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>https://www.uniroma1.it</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr"/>
+      <c r="P156" t="inlineStr"/>
+      <c r="Q156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Huazhong University of Science and Technology</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>http://english.hust.edu.cn/</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Politecnico di Milano</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>https://polimi.it</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Sichuan University</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>https://scu.edu.cn</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Sun Yat-sen University</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>https://www.sysu.edu.cn</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Xi'an Jiaotong University</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>https://www.xjtu.edu.cn</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Central South University</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>https://www.csu.edu.cn</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Universidade Estadual de Campinas (UNICAMP)</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>https://www.unicamp.br</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr"/>
+      <c r="Q163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Shandong University</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>https://www.sdu.edu.cn</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr"/>
+      <c r="Q164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>University of Bristol</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>https://www.bristol.ac.uk/</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr"/>
+      <c r="P165" t="inlineStr"/>
+      <c r="Q165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>University of Science and Technology of China</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>https://ustc.edu.cn</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr"/>
+      <c r="P166" t="inlineStr"/>
+      <c r="Q166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>University of Glasgow</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>https://www.gla.ac.uk/</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr"/>
+      <c r="P167" t="inlineStr"/>
+      <c r="Q167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Nanyang Technological University</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>https://www.ntu.edu.sg</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr"/>
+      <c r="P168" t="inlineStr"/>
+      <c r="Q168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr"/>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>University of Calgary</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>https://www.ucalgary.ca</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr"/>
+      <c r="P169" t="inlineStr"/>
+      <c r="Q169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>University of Leeds</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>https://www.leeds.ac.uk</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr"/>
+      <c r="P170" t="inlineStr"/>
+      <c r="Q170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr"/>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Southeast University</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>https://www.seu.edu.cn</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr"/>
+      <c r="P171" t="inlineStr"/>
+      <c r="Q171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr"/>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>University of Bonn</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>https://www.uni-bonn.de</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr"/>
+      <c r="P172" t="inlineStr"/>
+      <c r="Q172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr"/>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Newcastle University</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>https://www.ncl.ac.uk</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr"/>
+      <c r="P173" t="inlineStr"/>
+      <c r="Q173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr"/>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>University of Nottingham</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>https://www.nottingham.ac.uk/</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr"/>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>University of Sheffield</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>https://www.sheffield.ac.uk</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr"/>
+      <c r="Q175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr"/>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Aix-Marseille Université</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>https://www.univ-amu.fr/</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr"/>
+      <c r="Q176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr"/>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>University of Hong Kong</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>https://www.hku.hk</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr"/>
+      <c r="Q177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr"/>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Karlsruhe Institute of Technology</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>https://www.kit.edu</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr"/>
+      <c r="Q178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr"/>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Chinese University of Hong Kong</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>https://www.cuhk.edu.hk/</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr"/>
+      <c r="Q179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>University of Southampton</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>https://www.southampton.ac.uk/</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr"/>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>National Taiwan University</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>https://www.ntu.edu.tw/</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr"/>
+      <c r="P181" t="inlineStr"/>
+      <c r="Q181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr"/>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Jilin University</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>https://www.jlu.edu.cn/</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr"/>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>University of Naples Federico II</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>https://www.unina.it</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr"/>
+      <c r="P183" t="inlineStr"/>
+      <c r="Q183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr"/>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Tianjin University</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>https://www.tju.edu.cn/</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr"/>
+      <c r="P184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr"/>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>University of Ottawa</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>https://www.uottawa.ca</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr"/>
+      <c r="P185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr"/>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>The University of Western Australia</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>https://www.uwa.edu.au</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr"/>
+      <c r="P186" t="inlineStr"/>
+      <c r="Q186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr"/>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Friedrich-Alexander-Universität Erlangen-Nürnberg</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>https://www.fau.de/</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr"/>
+      <c r="P187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr"/>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Université Paris-Saclay</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>https://www.universite-paris-saclay.fr/</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr"/>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>University of Stuttgart</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>https://www.uni-stuttgart.de/</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr"/>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr"/>
+      <c r="P189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr"/>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Beihang University</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>https://buaa.edu.cn</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" t="inlineStr"/>
+      <c r="Q190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr"/>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Universidade do Porto</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>https://www.up.pt</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr"/>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Université Pierre-et-Marie-Curie</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr"/>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Hong Kong Polytechnic University</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>https://www.polyu.edu.hk/</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr"/>
+      <c r="P193" t="inlineStr"/>
+      <c r="Q193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Université de Lorraine</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>https://www.univ-lorraine.fr</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr"/>
+      <c r="P194" t="inlineStr"/>
+      <c r="Q194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>University of Florence</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>https://www.unifi.it</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr"/>
+      <c r="P195" t="inlineStr"/>
+      <c r="Q195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>South China University of Technology</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>http://www.scut.edu.cn</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr"/>
+      <c r="P196" t="inlineStr"/>
+      <c r="Q196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>University of Electronic Science and Technology of China</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>https://www.uestc.edu.cn</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr"/>
+      <c r="P197" t="inlineStr"/>
+      <c r="Q197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>King Saud University</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>https://ksu.edu.sa</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr"/>
+      <c r="P198" t="inlineStr"/>
+      <c r="Q198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>University of Münster</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>https://www.uni-muenster.de/</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr"/>
+      <c r="P199" t="inlineStr"/>
+      <c r="Q199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr"/>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>École Polytechnique Fédérale de Lausanne</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>https://www.epfl.ch/</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr"/>
+      <c r="P200" t="inlineStr"/>
+      <c r="Q200" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -8775,23 +8775,35 @@
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr">
         <is>
-          <t>https://www.cam.ac.uk</t>
+          <t>https://openalex.org/A5085582572</t>
         </is>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O151" t="inlineStr"/>
-      <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>M. J. Allen</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Antenna Design for Indoor Positioning Systems: Challenges and Solutions (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr"/>
@@ -8814,23 +8826,35 @@
       <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>https://www.imperial.ac.uk</t>
+          <t>https://openalex.org/A5039289964</t>
         </is>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O152" t="inlineStr"/>
-      <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Geoffrey Ye Li</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>CSI-Fingerprinting Indoor Localization via Attention-Augmented Residual Convolutional Neural Network (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr"/>
@@ -8853,23 +8877,35 @@
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>https://www.ucas.ac.cn</t>
+          <t>https://openalex.org/A5100376373</t>
         </is>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O153" t="inlineStr"/>
-      <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Zhi Wang</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>UWBLoc: NLoS Mitigation for Practical UWB Localization (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr"/>
@@ -8890,25 +8926,33 @@
       <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>https://www.osaka-u.ac.jp</t>
-        </is>
-      </c>
+      <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O154" t="inlineStr"/>
-      <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Moustafa Youssef</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>MambaLoc: Lightweight Indoor Localization For Unmanned Vehicles Using Cross-Modal Knowledge Distillation (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr"/>
@@ -8931,23 +8975,35 @@
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr">
         <is>
-          <t>https://www.manchester.ac.uk/</t>
+          <t>https://openalex.org/A5068254239</t>
         </is>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O155" t="inlineStr"/>
-      <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Mehmet Kemal Özdemir</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>Cyber-WISE: A Cyber-Physical Deep Wireless Indoor Positioning System and Digital Twin Approach (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr"/>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -9026,23 +9026,35 @@
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>https://www.uniroma1.it</t>
+          <t>https://openalex.org/A5062526081</t>
         </is>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O156" t="inlineStr"/>
-      <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Maria‐Gabriella Di Benedetto</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>Efficient CNN-Based Classification of NLOS/LOS Conditions Using CIR Features in Ultra-Wideband Networks (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr"/>
@@ -9065,23 +9077,35 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>http://english.hust.edu.cn/</t>
+          <t>https://openalex.org/A5100678341</t>
         </is>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O157" t="inlineStr"/>
-      <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Tao Jiang</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>AutoLoc: Toward Ubiquitous AoA-Based Indoor Localization Using Commodity WiFi (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr"/>
@@ -9104,23 +9128,35 @@
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
-          <t>https://polimi.it</t>
+          <t>https://openalex.org/A5118128066</t>
         </is>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O158" t="inlineStr"/>
-      <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Arimondo Scrivano</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>Advances in Indoor Positioning Systems: Integrating IoT and Machine Learning for Enhanced Accuracy (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr"/>
@@ -9143,23 +9179,35 @@
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
-          <t>https://scu.edu.cn</t>
+          <t>https://openalex.org/A5038871254</t>
         </is>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O159" t="inlineStr"/>
-      <c r="P159" t="inlineStr"/>
-      <c r="Q159" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Yanbing Yang</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>Leveraging Hybrid RF-VLP for High-Accuracy Indoor Localization with Sparse Anchors (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr"/>
@@ -9182,23 +9230,35 @@
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr">
         <is>
-          <t>https://www.sysu.edu.cn</t>
+          <t>https://openalex.org/A5100728341</t>
         </is>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O160" t="inlineStr"/>
-      <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Y. B. Zhao</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>Ranging Error model for IEEE 802.15.4 based UWB IoT devices (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr"/>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -9281,23 +9281,35 @@
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
-          <t>https://www.xjtu.edu.cn</t>
+          <t>https://openalex.org/A5102551596</t>
         </is>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O161" t="inlineStr"/>
-      <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Qingkai Wang</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>Spatio-temporal feature fusion model based on Attention mechanism for RFID indoor positioning (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr"/>
@@ -9320,23 +9332,35 @@
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>https://www.csu.edu.cn</t>
+          <t>https://openalex.org/A5000926804</t>
         </is>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O162" t="inlineStr"/>
-      <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Chizhou Zhang</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>1D-CLANet: A Novel Network for NLoS Classification in UWB Indoor Positioning System (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr"/>
@@ -9359,23 +9383,35 @@
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr">
         <is>
-          <t>https://www.unicamp.br</t>
+          <t>https://openalex.org/A5059696610</t>
         </is>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O163" t="inlineStr"/>
-      <c r="P163" t="inlineStr"/>
-      <c r="Q163" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>André Leon Sampaio Gradvohl</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>Studies on indoor positioning algorithms using BLE Beacons (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr"/>
@@ -9398,23 +9434,35 @@
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
-          <t>https://www.sdu.edu.cn</t>
+          <t>https://openalex.org/A5110210243</t>
         </is>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O164" t="inlineStr"/>
-      <c r="P164" t="inlineStr"/>
-      <c r="Q164" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Jianping Xing</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>Application of variational Bayesian-based cubature information filter for UWB/INS tightly coupled positioning system (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr"/>
@@ -9437,23 +9485,35 @@
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
-          <t>https://www.bristol.ac.uk/</t>
+          <t>https://openalex.org/A5026442244</t>
         </is>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O165" t="inlineStr"/>
-      <c r="P165" t="inlineStr"/>
-      <c r="Q165" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Eli De Poorter</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>Transfer Learning for UWB Error Correction and (N)LOS Classification in Multiple Environments (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr"/>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q200"/>
+  <dimension ref="A1:Q250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10876,6 +10876,1956 @@
       <c r="P200" t="inlineStr"/>
       <c r="Q200" t="inlineStr"/>
     </row>
+    <row r="201">
+      <c r="A201" t="inlineStr"/>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Huazhong University of Science and Technology</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>http://english.hust.edu.cn/</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr"/>
+      <c r="P201" t="inlineStr"/>
+      <c r="Q201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr"/>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>University of Science and Technology of China</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>https://ustc.edu.cn</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr"/>
+      <c r="P202" t="inlineStr"/>
+      <c r="Q202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr"/>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>University of Electronic Science and Technology of China</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>https://www.uestc.edu.cn</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr"/>
+      <c r="P203" t="inlineStr"/>
+      <c r="Q203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr"/>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Queen Mary University of London</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>https://www.qmul.ac.uk/</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr"/>
+      <c r="P204" t="inlineStr"/>
+      <c r="Q204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr"/>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Technische Universität Dresden</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>https://tu-dresden.de</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr"/>
+      <c r="P205" t="inlineStr"/>
+      <c r="Q205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr"/>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Beijing Institute of Technology</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>https://bit.edu.cn</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr"/>
+      <c r="P206" t="inlineStr"/>
+      <c r="Q206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr"/>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Northwestern Polytechnical University</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>https://www.nwpu.edu.cn</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr"/>
+      <c r="P207" t="inlineStr"/>
+      <c r="Q207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr"/>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>UCLouvain</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>https://uclouvain.be</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr"/>
+      <c r="P208" t="inlineStr"/>
+      <c r="Q208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr"/>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>University of Auckland</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>https://www.auckland.ac.nz/en.html</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr"/>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr"/>
+      <c r="P209" t="inlineStr"/>
+      <c r="Q209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr"/>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Chongqing University</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>https://www.cqu.edu.cn</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr"/>
+      <c r="P210" t="inlineStr"/>
+      <c r="Q210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr"/>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Dalian University of Technology</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>https://www.dlut.edu.cn</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr"/>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr"/>
+      <c r="P211" t="inlineStr"/>
+      <c r="Q211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr"/>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Zhengzhou University</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>https://www.zzu.edu.cn</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr"/>
+      <c r="P212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr"/>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Ruhr University Bochum</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>https://www.ruhr-uni-bochum.de</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr"/>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr"/>
+      <c r="P213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr"/>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Friedrich Schiller University Jena</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>https://www.uni-jena.de/en</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr"/>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr"/>
+      <c r="P214" t="inlineStr"/>
+      <c r="Q214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr"/>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Hiroshima University</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>http://www.hiroshima-u.ac.jp/index.html</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr"/>
+      <c r="P215" t="inlineStr"/>
+      <c r="Q215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr"/>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>University of Belgrade</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>http://www.bg.ac.rs/en/</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr"/>
+      <c r="P216" t="inlineStr"/>
+      <c r="Q216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr"/>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Lyon 1 Université</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>https://www.univ-lyon1.fr</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr"/>
+      <c r="P217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr"/>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Santa Catarina</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>http://en.ufsc.br/</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr"/>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr"/>
+      <c r="P218" t="inlineStr"/>
+      <c r="Q218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr"/>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Xiamen University</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>https://www.xmu.edu.cn</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr"/>
+      <c r="P219" t="inlineStr"/>
+      <c r="Q219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr"/>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Technion – Israel Institute of Technology</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>http://www.technion.ac.il/</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr"/>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr"/>
+      <c r="P220" t="inlineStr"/>
+      <c r="Q220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr"/>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Queen's University</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>https://www.queensu.ca/</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr"/>
+      <c r="P221" t="inlineStr"/>
+      <c r="Q221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr"/>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>University of Zagreb</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>http://www.unizg.hr/</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr"/>
+      <c r="P222" t="inlineStr"/>
+      <c r="Q222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr"/>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>University of Manitoba</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>https://umanitoba.ca</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr"/>
+      <c r="P223" t="inlineStr"/>
+      <c r="Q223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr"/>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Korea Advanced Institute of Science and Technology</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>https://www.kaist.ac.kr</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr"/>
+      <c r="P224" t="inlineStr"/>
+      <c r="Q224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr"/>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>China University of Geosciences</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>https://www.cug.edu.cn/</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr"/>
+      <c r="P225" t="inlineStr"/>
+      <c r="Q225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr"/>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>TU Wien</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>https://www.tuwien.at</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr"/>
+      <c r="P226" t="inlineStr"/>
+      <c r="Q226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr"/>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Universidad de Sevilla</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>https://www.us.es/</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr"/>
+      <c r="P227" t="inlineStr"/>
+      <c r="Q227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr"/>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Queen's University Belfast</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>https://www.qub.ac.uk</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr"/>
+      <c r="P228" t="inlineStr"/>
+      <c r="Q228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr"/>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Nankai University</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>https://nankai.edu.cn</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr"/>
+      <c r="P229" t="inlineStr"/>
+      <c r="Q229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr"/>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Soochow University</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>https://www.suda.edu.cn</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr"/>
+      <c r="P230" t="inlineStr"/>
+      <c r="Q230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr"/>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Aristotle University of Thessaloniki</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>https://www.auth.gr</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr"/>
+      <c r="P231" t="inlineStr"/>
+      <c r="Q231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr"/>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Dalhousie University</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>https://www.dal.ca</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr"/>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr"/>
+      <c r="P232" t="inlineStr"/>
+      <c r="Q232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr"/>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>University of Malaya</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>https://www.um.edu.my/</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr"/>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr"/>
+      <c r="P233" t="inlineStr"/>
+      <c r="Q233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr"/>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Université Paris Diderot</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>http://www.univ-paris-diderot.fr/sc/site.php?bc=accueil&amp;np=accueil</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr"/>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr"/>
+      <c r="P234" t="inlineStr"/>
+      <c r="Q234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr"/>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Universidade Federal de Pernambuco</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>https://www.ufpe.br</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr"/>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr"/>
+      <c r="P235" t="inlineStr"/>
+      <c r="Q235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr"/>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>University of York</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>https://www.york.ac.uk</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr"/>
+      <c r="P236" t="inlineStr"/>
+      <c r="Q236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr"/>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Kobe University</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>http://www.kobe-u.ac.jp/en/alumni/index.html</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr"/>
+      <c r="P237" t="inlineStr"/>
+      <c r="Q237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr"/>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Medical University of Vienna</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>https://www.meduniwien.ac.at</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr"/>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr"/>
+      <c r="P238" t="inlineStr"/>
+      <c r="Q238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr"/>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Université de Toulouse</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>https://www.univ-tlse3.fr</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr"/>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr"/>
+      <c r="P239" t="inlineStr"/>
+      <c r="Q239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr"/>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Shanghai University</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>https://www.shu.edu.cn</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr"/>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr"/>
+      <c r="P240" t="inlineStr"/>
+      <c r="Q240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr"/>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>University of the Basque Country</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>https://www.ehu.eus</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr"/>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr"/>
+      <c r="P241" t="inlineStr"/>
+      <c r="Q241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr"/>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>University of Ljubljana</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>https://www.uni-lj.si/</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr"/>
+      <c r="P242" t="inlineStr"/>
+      <c r="Q242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr"/>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>King Abdulaziz University</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>https://www.kau.edu.sa/</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr"/>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr"/>
+      <c r="P243" t="inlineStr"/>
+      <c r="Q243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr"/>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>University of Science and Technology Beijing</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>https://www.ustb.edu.cn</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr"/>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr"/>
+      <c r="P244" t="inlineStr"/>
+      <c r="Q244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr"/>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>National Cheng Kung University</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>https://web.ncku.edu.tw/</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr"/>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr"/>
+      <c r="P245" t="inlineStr"/>
+      <c r="Q245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr"/>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Université Toulouse III - Paul Sabatier</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>http://www.univ-tlse3.fr/</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr"/>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr"/>
+      <c r="P246" t="inlineStr"/>
+      <c r="Q246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr"/>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Universidad Nacional de Colombia</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
+      <c r="J247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>https://unal.edu.co</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr"/>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr"/>
+      <c r="P247" t="inlineStr"/>
+      <c r="Q247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr"/>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>St Petersburg University</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
+      <c r="J248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>https://spbu.ru/</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr"/>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr"/>
+      <c r="P248" t="inlineStr"/>
+      <c r="Q248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr"/>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Shenzhen University</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
+      <c r="J249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>https://www.szu.edu.cn</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr"/>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr"/>
+      <c r="P249" t="inlineStr"/>
+      <c r="Q249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr"/>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>University of Coimbra</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
+      <c r="J250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>https://www.uc.pt</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr"/>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr"/>
+      <c r="P250" t="inlineStr"/>
+      <c r="Q250" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -9536,23 +9536,35 @@
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
-          <t>https://ustc.edu.cn</t>
+          <t>https://openalex.org/A5100678341</t>
         </is>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O166" t="inlineStr"/>
-      <c r="P166" t="inlineStr"/>
-      <c r="Q166" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Tao Jiang</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>AutoLoc: Toward Ubiquitous AoA-Based Indoor Localization Using Commodity WiFi (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr"/>
@@ -9575,23 +9587,35 @@
       <c r="J167" t="inlineStr"/>
       <c r="K167" t="inlineStr">
         <is>
-          <t>https://www.gla.ac.uk/</t>
+          <t>https://openalex.org/A5059152392</t>
         </is>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O167" t="inlineStr"/>
-      <c r="P167" t="inlineStr"/>
-      <c r="Q167" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Konstantinos N. Plataniotis</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>Enhancing LOS/NLOS Classification in UWB with Robust Feature Engineering (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr"/>
@@ -9614,23 +9638,35 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
-          <t>https://www.ntu.edu.sg</t>
+          <t>https://openalex.org/A5023142347</t>
         </is>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O168" t="inlineStr"/>
-      <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>U-Xuan Tan</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>Localization through mitigating and compensating UWB NLOS ranging error with neural network (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr"/>
@@ -9653,23 +9689,35 @@
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
-          <t>https://www.ucalgary.ca</t>
+          <t>https://openalex.org/A5008779348</t>
         </is>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O169" t="inlineStr"/>
-      <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Behrouz H. Far</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>Transformer-Based UWB Positioning: Learning to Correct Ranging Errors for Autonomous Agents (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr"/>
@@ -9690,25 +9738,33 @@
       <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>https://www.leeds.ac.uk</t>
-        </is>
-      </c>
+      <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O170" t="inlineStr"/>
-      <c r="P170" t="inlineStr"/>
-      <c r="Q170" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Yuanyou Zuo</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>The Application of Bluetooth Technology in Indoor Navigation (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr"/>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -9787,23 +9787,35 @@
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
-          <t>https://www.seu.edu.cn</t>
+          <t>https://openalex.org/A5043390157</t>
         </is>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O171" t="inlineStr"/>
-      <c r="P171" t="inlineStr"/>
-      <c r="Q171" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Chee Kiat Seow</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>Ultra-Wideband Ranging Error Mitigation with Novel Channel Impulse Response Feature Parameters and Two-Step Non-Line-of-Sight Identification (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr"/>
@@ -9826,23 +9838,35 @@
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
-          <t>https://www.uni-bonn.de</t>
+          <t>https://openalex.org/A5011166267</t>
         </is>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O172" t="inlineStr"/>
-      <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Cyrill Stachniss</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>Improving Indoor Localization Accuracy by Using an Efficient Implicit Neural Map Representation (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr"/>
@@ -9865,23 +9889,35 @@
       <c r="J173" t="inlineStr"/>
       <c r="K173" t="inlineStr">
         <is>
-          <t>https://www.ncl.ac.uk</t>
+          <t>https://openalex.org/A5005190949</t>
         </is>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O173" t="inlineStr"/>
-      <c r="P173" t="inlineStr"/>
-      <c r="Q173" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Muhammad Shafique</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>On the Application of Efficient Neural Mapping to Real-Time Indoor Localisation for Unmanned Ground Vehicles (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr"/>
@@ -9902,25 +9938,33 @@
       <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr"/>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>https://www.nottingham.ac.uk/</t>
-        </is>
-      </c>
+      <c r="K174" t="inlineStr"/>
       <c r="L174" t="inlineStr"/>
       <c r="M174" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O174" t="inlineStr"/>
-      <c r="P174" t="inlineStr"/>
-      <c r="Q174" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Mingyue Ding</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>Cloud &amp; IoT based indoor positioning solution with intuitive AR guidance (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr"/>
@@ -9943,23 +9987,35 @@
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
-          <t>https://www.sheffield.ac.uk</t>
+          <t>https://openalex.org/A5020365363</t>
         </is>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O175" t="inlineStr"/>
-      <c r="P175" t="inlineStr"/>
-      <c r="Q175" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Yan Yan Farm</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>Evaluation of Theoretical and Empirical Log-Normal Models for Wi-Fi Fingerprint Mapping in Indoor Positioning (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr"/>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -10038,23 +10038,35 @@
       <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>https://www.univ-amu.fr/</t>
+          <t>https://openalex.org/A5049635426</t>
         </is>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O176" t="inlineStr"/>
-      <c r="P176" t="inlineStr"/>
-      <c r="Q176" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>F. Bentosela</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>Analysing the Scattering of Electromagnetic Ultra-wideband Pulses from Large-Scale Objects by the Use of Wavelets (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr"/>
@@ -10077,23 +10089,35 @@
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
-          <t>https://www.hku.hk</t>
+          <t>https://openalex.org/A5057049452</t>
         </is>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O177" t="inlineStr"/>
-      <c r="P177" t="inlineStr"/>
-      <c r="Q177" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>S. C. Chan</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>A Learning-Enhanced Robust Adaptive Fading Extended/Error-State Kalman Filter for Integrated IMU-UWB Indoor Localization Under NLOS Reception (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr"/>
@@ -10116,23 +10140,35 @@
       <c r="J178" t="inlineStr"/>
       <c r="K178" t="inlineStr">
         <is>
-          <t>https://www.kit.edu</t>
+          <t>https://openalex.org/A5021007726</t>
         </is>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O178" t="inlineStr"/>
-      <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Christof Weinhardt</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>Augmented Reality-based Indoor Positioning for Smart Home Automations (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr"/>
@@ -10155,23 +10191,35 @@
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
-          <t>https://www.cuhk.edu.hk/</t>
+          <t>https://openalex.org/A5137647837</t>
         </is>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O179" t="inlineStr"/>
-      <c r="P179" t="inlineStr"/>
-      <c r="Q179" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>He Chen</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>CIRSense: Rethinking WiFi Sensing With Channel Impulse Response (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr"/>
@@ -10194,23 +10242,35 @@
       <c r="J180" t="inlineStr"/>
       <c r="K180" t="inlineStr">
         <is>
-          <t>https://www.southampton.ac.uk/</t>
+          <t>https://openalex.org/A5091122305</t>
         </is>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O180" t="inlineStr"/>
-      <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Lajos Hanzo</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>Indoor Localization and Tracking in Reconfigurable Intelligent Surface Aided mmWave Systems (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr"/>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -10293,23 +10293,35 @@
       <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
-          <t>https://www.ntu.edu.tw/</t>
+          <t>https://openalex.org/A5102935450</t>
         </is>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O181" t="inlineStr"/>
-      <c r="P181" t="inlineStr"/>
-      <c r="Q181" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Yi‐Ping Hung</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>VIUNet: Deep Visual–Inertial–UWB Fusion for Indoor UAV Localization (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr"/>
@@ -10332,23 +10344,35 @@
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
-          <t>https://www.jlu.edu.cn/</t>
+          <t>https://openalex.org/A5044497830</t>
         </is>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O182" t="inlineStr"/>
-      <c r="P182" t="inlineStr"/>
-      <c r="Q182" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Jinxin Liu</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>NetLib Ranging Framework Based on UWB (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr"/>
@@ -10371,23 +10395,35 @@
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
-          <t>https://www.unina.it</t>
+          <t>https://openalex.org/A5026144426</t>
         </is>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O183" t="inlineStr"/>
-      <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Aldo Zollo</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>A Proposal for a VR Serious Game for Training of Earthquake Early Warning Systems for Wearable Devices in the Context of Critical Environments (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr"/>
@@ -10410,23 +10446,35 @@
       <c r="J184" t="inlineStr"/>
       <c r="K184" t="inlineStr">
         <is>
-          <t>https://www.tju.edu.cn/</t>
+          <t>https://openalex.org/A5084469256</t>
         </is>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O184" t="inlineStr"/>
-      <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Yuxiang Han</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>A New Method for Enhancing the Robustness of Close-Range Targets Imaging Based on UWB (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr"/>
@@ -10449,23 +10497,35 @@
       <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>https://www.uottawa.ca</t>
+          <t>https://openalex.org/A5071725359</t>
         </is>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O185" t="inlineStr"/>
-      <c r="P185" t="inlineStr"/>
-      <c r="Q185" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Yishan Su</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>Attack-Resilient Secure Localization for Underwater Acoustic Networks via Frequency-Diverse DRSS (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr"/>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -10546,25 +10546,33 @@
       <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr"/>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>https://www.uwa.edu.au</t>
-        </is>
-      </c>
+      <c r="K186" t="inlineStr"/>
       <c r="L186" t="inlineStr"/>
       <c r="M186" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O186" t="inlineStr"/>
-      <c r="P186" t="inlineStr"/>
-      <c r="Q186" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Wang, Jiarui</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>Parkes observations for project P1375 semester 2026APRS_12 (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr"/>
@@ -10587,23 +10595,35 @@
       <c r="J187" t="inlineStr"/>
       <c r="K187" t="inlineStr">
         <is>
-          <t>https://www.fau.de/</t>
+          <t>https://openalex.org/A5023277657</t>
         </is>
       </c>
       <c r="L187" t="inlineStr"/>
       <c r="M187" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O187" t="inlineStr"/>
-      <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Christopher Mutschler</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>Non-Line-of-Sight Detection for Radio Localization using Deep State Space Models (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr"/>
@@ -10626,23 +10646,35 @@
       <c r="J188" t="inlineStr"/>
       <c r="K188" t="inlineStr">
         <is>
-          <t>https://www.universite-paris-saclay.fr/</t>
+          <t>https://openalex.org/A5060020877</t>
         </is>
       </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O188" t="inlineStr"/>
-      <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Chau Yuen</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>Fingerprinting Database Development Methods for Reconfigurable Intelligent Surface Assisted Indoor Positioning System (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr"/>
@@ -10665,23 +10697,35 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
-          <t>https://www.uni-stuttgart.de/</t>
+          <t>https://openalex.org/A5123631481</t>
         </is>
       </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O189" t="inlineStr"/>
-      <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Bin Yang</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>Investigation of ArUco Marker Placement for Planar Indoor Localization (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr"/>
@@ -10704,23 +10748,35 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>https://buaa.edu.cn</t>
+          <t>https://openalex.org/A5024150556</t>
         </is>
       </c>
       <c r="L190" t="inlineStr"/>
       <c r="M190" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O190" t="inlineStr"/>
-      <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Dongkai Yang</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>Fuzzy Comprehensive Evaluation based NLOS Identification for UWB Indoor Positioning (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr"/>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -10799,23 +10799,35 @@
       <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>https://www.up.pt</t>
+          <t>https://openalex.org/A5022725672</t>
         </is>
       </c>
       <c r="L191" t="inlineStr"/>
       <c r="M191" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O191" t="inlineStr"/>
-      <c r="P191" t="inlineStr"/>
-      <c r="Q191" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Pedro Costa</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>A Performance Comparison between Different Industrial Real-Time Indoor Localization Systems for Mobile Platforms (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr"/>
@@ -10836,21 +10848,37 @@
       <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>https://openalex.org/A5100656483</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr"/>
       <c r="M192" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O192" t="inlineStr"/>
-      <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>Wireless Sensing</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Chris J. Cotsapas</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>Genetic mapping across autoimmune diseases reveals shared associations and mechanisms (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr"/>
@@ -10873,23 +10901,35 @@
       <c r="J193" t="inlineStr"/>
       <c r="K193" t="inlineStr">
         <is>
-          <t>https://www.polyu.edu.hk/</t>
+          <t>https://openalex.org/A5058337483</t>
         </is>
       </c>
       <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O193" t="inlineStr"/>
-      <c r="P193" t="inlineStr"/>
-      <c r="Q193" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Henry K. Chu</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>UVIO: Adaptive Kalman Filtering UWB-Aided Visual-Inertial SLAM System for Complex Indoor Environments (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr"/>
@@ -10912,23 +10952,35 @@
       <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
-          <t>https://www.univ-lorraine.fr</t>
+          <t>https://openalex.org/A5056264312</t>
         </is>
       </c>
       <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O194" t="inlineStr"/>
-      <c r="P194" t="inlineStr"/>
-      <c r="Q194" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Cristóbal Carreño</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>Resilience Framework for the Availability of Indoor Location-Based Services in Constrained Environments (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr"/>
@@ -10951,23 +11003,35 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
-          <t>https://www.unifi.it</t>
+          <t>https://openalex.org/A5089835241</t>
         </is>
       </c>
       <c r="L195" t="inlineStr"/>
       <c r="M195" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O195" t="inlineStr"/>
-      <c r="P195" t="inlineStr"/>
-      <c r="Q195" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Lorenzo Mucchi</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>IN-Rep: A New Open Data Repository for AI-Based Positioning in Industrial Networks (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr"/>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -11054,23 +11054,35 @@
       <c r="J196" t="inlineStr"/>
       <c r="K196" t="inlineStr">
         <is>
-          <t>http://www.scut.edu.cn</t>
+          <t>https://openalex.org/A5102800304</t>
         </is>
       </c>
       <c r="L196" t="inlineStr"/>
       <c r="M196" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O196" t="inlineStr"/>
-      <c r="P196" t="inlineStr"/>
-      <c r="Q196" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Hailong Pei</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>UWB Anchor Self-Localization Algorithm Based on PDOA and TOF (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr"/>
@@ -11093,23 +11105,35 @@
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
-          <t>https://www.uestc.edu.cn</t>
+          <t>https://openalex.org/A5101989539</t>
         </is>
       </c>
       <c r="L197" t="inlineStr"/>
       <c r="M197" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O197" t="inlineStr"/>
-      <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Gang Feng</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>An Adapted Mean Teacher Model for Semi-supervised Indoor Positioning using Channel Impulse Response (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr"/>
@@ -11132,23 +11156,35 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
-          <t>https://ksu.edu.sa</t>
+          <t>https://openalex.org/A5070109697</t>
         </is>
       </c>
       <c r="L198" t="inlineStr"/>
       <c r="M198" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O198" t="inlineStr"/>
-      <c r="P198" t="inlineStr"/>
-      <c r="Q198" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Essam A. Al‐Ammar</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>A Novel Self-Calibrated UWB-Based Indoor Localization Systems for Context-Aware Applications (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr"/>
@@ -11171,23 +11207,35 @@
       <c r="J199" t="inlineStr"/>
       <c r="K199" t="inlineStr">
         <is>
-          <t>https://www.uni-muenster.de/</t>
+          <t>https://openalex.org/A5072493587</t>
         </is>
       </c>
       <c r="L199" t="inlineStr"/>
       <c r="M199" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O199" t="inlineStr"/>
-      <c r="P199" t="inlineStr"/>
-      <c r="Q199" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Martin Tomko</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>A Visibility‐Based Multitree of a Space Subdivision for Indoor Localization (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr"/>
@@ -11210,23 +11258,35 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>https://www.epfl.ch/</t>
+          <t>https://openalex.org/A5059133771</t>
         </is>
       </c>
       <c r="L200" t="inlineStr"/>
       <c r="M200" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O200" t="inlineStr"/>
-      <c r="P200" t="inlineStr"/>
-      <c r="Q200" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>Andreas Peter Burg</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>Single-Anchor UWB Localization Using Channel Impulse Response Distributions (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr"/>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q250"/>
+  <dimension ref="A1:Q300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13238,6 +13238,1956 @@
       <c r="P250" t="inlineStr"/>
       <c r="Q250" t="inlineStr"/>
     </row>
+    <row r="251">
+      <c r="A251" t="inlineStr"/>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Huazhong University of Science and Technology</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
+      <c r="J251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>http://english.hust.edu.cn/</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr"/>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr"/>
+      <c r="P251" t="inlineStr"/>
+      <c r="Q251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr"/>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>University of Science and Technology of China</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
+      <c r="J252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>https://ustc.edu.cn</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr"/>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr"/>
+      <c r="P252" t="inlineStr"/>
+      <c r="Q252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr"/>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>University of Electronic Science and Technology of China</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
+      <c r="J253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>https://www.uestc.edu.cn</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr"/>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr"/>
+      <c r="P253" t="inlineStr"/>
+      <c r="Q253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr"/>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Korea Advanced Institute of Science and Technology</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
+      <c r="J254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>https://www.kaist.ac.kr</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr"/>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr"/>
+      <c r="P254" t="inlineStr"/>
+      <c r="Q254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr"/>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>University of Science and Technology Beijing</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr"/>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
+      <c r="J255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>https://www.ustb.edu.cn</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr"/>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr"/>
+      <c r="P255" t="inlineStr"/>
+      <c r="Q255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr"/>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Ben-Gurion University of the Negev</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Israel</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
+      <c r="J256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>https://www.bgu.ac.il</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr"/>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr"/>
+      <c r="P256" t="inlineStr"/>
+      <c r="Q256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr"/>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>University of Pavia</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
+      <c r="J257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>https://portale.unipv.it/it</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr"/>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr"/>
+      <c r="P257" t="inlineStr"/>
+      <c r="Q257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr"/>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Hunan University</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>https://www.hnu.edu.cn</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr"/>
+      <c r="P258" t="inlineStr"/>
+      <c r="Q258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr"/>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Griffith University</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
+      <c r="J259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>https://www.griffith.edu.au</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr"/>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr"/>
+      <c r="P259" t="inlineStr"/>
+      <c r="Q259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr"/>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Curtin University</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
+      <c r="J260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>https://www.curtin.edu.au</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr"/>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr"/>
+      <c r="P260" t="inlineStr"/>
+      <c r="Q260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr"/>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Technische Universität Darmstadt</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
+      <c r="J261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>https://www.tu-darmstadt.de</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr"/>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr"/>
+      <c r="P261" t="inlineStr"/>
+      <c r="Q261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr"/>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>University of Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr"/>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
+      <c r="J262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>https://www.usask.ca/</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr"/>
+      <c r="P262" t="inlineStr"/>
+      <c r="Q262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr"/>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Hong Kong University of Science and Technology</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr"/>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr"/>
+      <c r="J263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>https://hkust.edu.hk</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr"/>
+      <c r="P263" t="inlineStr"/>
+      <c r="Q263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr"/>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Southern Medical University</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr"/>
+      <c r="J264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>https://www.smu.edu.cn</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr"/>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr"/>
+      <c r="P264" t="inlineStr"/>
+      <c r="Q264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr"/>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Universiti Sains Malaysia</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr"/>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr"/>
+      <c r="J265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>https://www.usm.my</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr"/>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr"/>
+      <c r="P265" t="inlineStr"/>
+      <c r="Q265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr"/>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Nanjing University of Aeronautics and Astronautics</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr"/>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>https://www.nuaa.edu.cn</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr"/>
+      <c r="P266" t="inlineStr"/>
+      <c r="Q266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr"/>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>University of Technology Sydney</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr"/>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr"/>
+      <c r="J267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>https://www.uts.edu.au</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr"/>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr"/>
+      <c r="P267" t="inlineStr"/>
+      <c r="Q267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr"/>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>National University of Malaysia</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr"/>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr"/>
+      <c r="J268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>https://www.ukm.my</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr"/>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr"/>
+      <c r="P268" t="inlineStr"/>
+      <c r="Q268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr"/>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Deakin University</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr"/>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr"/>
+      <c r="J269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>https://www.deakin.edu.au</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr"/>
+      <c r="P269" t="inlineStr"/>
+      <c r="Q269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr"/>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>National Yang Ming Chiao Tung University</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr"/>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr"/>
+      <c r="J270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>https://www.nycu.edu.tw/</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr"/>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr"/>
+      <c r="P270" t="inlineStr"/>
+      <c r="Q270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr"/>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>China Agricultural University</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr"/>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr"/>
+      <c r="J271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>https://en.cau.edu.cn/</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr"/>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr"/>
+      <c r="P271" t="inlineStr"/>
+      <c r="Q271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr"/>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Wuhan University of Technology</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" t="inlineStr"/>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr"/>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>https://www.whut.edu.cn</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr"/>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr"/>
+      <c r="P272" t="inlineStr"/>
+      <c r="Q272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr"/>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Universität Ulm</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr"/>
+      <c r="E273" t="inlineStr"/>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>https://www.uni-ulm.de</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr"/>
+      <c r="P273" t="inlineStr"/>
+      <c r="Q273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr"/>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Medizinische Hochschule Hannover</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="inlineStr"/>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>https://www.mhh.de</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr"/>
+      <c r="P274" t="inlineStr"/>
+      <c r="Q274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr"/>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Universitat Politècnica de Catalunya</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="inlineStr"/>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr"/>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>https://www.upc.edu</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr"/>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr"/>
+      <c r="P275" t="inlineStr"/>
+      <c r="Q275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr"/>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Queensland University of Technology</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr"/>
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>https://www.qut.edu.au/</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr"/>
+      <c r="P276" t="inlineStr"/>
+      <c r="Q276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr"/>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Indian Institute of Science Bangalore</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>https://www.iisc.ac.in/</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr"/>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr"/>
+      <c r="P277" t="inlineStr"/>
+      <c r="Q277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr"/>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Nantes Université</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="inlineStr"/>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr"/>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>https://www.univ-nantes.fr/</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr"/>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr"/>
+      <c r="P278" t="inlineStr"/>
+      <c r="Q278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr"/>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>National University of Defense Technology</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr"/>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr"/>
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>https://www.nudt.edu.cn/</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr"/>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr"/>
+      <c r="P279" t="inlineStr"/>
+      <c r="Q279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr"/>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Jiangsu University</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="inlineStr"/>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr"/>
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>https://www.ujs.edu.cn</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr"/>
+      <c r="P280" t="inlineStr"/>
+      <c r="Q280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr"/>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Lancaster University</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr"/>
+      <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>https://www.lancaster.ac.uk</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr"/>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr"/>
+      <c r="P281" t="inlineStr"/>
+      <c r="Q281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr"/>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Jinan University</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr"/>
+      <c r="J282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>https://english.jnu.edu.cn/</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr"/>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr"/>
+      <c r="P282" t="inlineStr"/>
+      <c r="Q282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr"/>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Université de Rennes</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="inlineStr"/>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr"/>
+      <c r="H283" t="inlineStr"/>
+      <c r="I283" t="inlineStr"/>
+      <c r="J283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>https://www.univ-rennes.fr</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr"/>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr"/>
+      <c r="P283" t="inlineStr"/>
+      <c r="Q283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr"/>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Simon Fraser University</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr"/>
+      <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr"/>
+      <c r="J284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>https://www.sfu.ca</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr"/>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr"/>
+      <c r="P284" t="inlineStr"/>
+      <c r="Q284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr"/>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Pontificia Universidad Católica de Chile</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr"/>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr"/>
+      <c r="H285" t="inlineStr"/>
+      <c r="I285" t="inlineStr"/>
+      <c r="J285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>https://www.uc.cl/</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr"/>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr"/>
+      <c r="P285" t="inlineStr"/>
+      <c r="Q285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr"/>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Xidian University</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="inlineStr"/>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr"/>
+      <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr"/>
+      <c r="J286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>https://www.xidian.edu.cn</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr"/>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr"/>
+      <c r="P286" t="inlineStr"/>
+      <c r="Q286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr"/>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Universitas Gadjah Mada</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="inlineStr"/>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr"/>
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr"/>
+      <c r="J287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>https://ugm.ac.id</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr"/>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr"/>
+      <c r="P287" t="inlineStr"/>
+      <c r="Q287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr"/>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>University of Strathclyde</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" t="inlineStr"/>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr"/>
+      <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr"/>
+      <c r="J288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>https://www.strath.ac.uk</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr"/>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr"/>
+      <c r="P288" t="inlineStr"/>
+      <c r="Q288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr"/>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Nanjing University of Science and Technology</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr"/>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr"/>
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr"/>
+      <c r="J289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>https://www.njust.edu.cn</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr"/>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr"/>
+      <c r="P289" t="inlineStr"/>
+      <c r="Q289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr"/>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>University of Bari Aldo Moro</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="inlineStr"/>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr"/>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr"/>
+      <c r="J290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>https://www.uniba.it</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr"/>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr"/>
+      <c r="P290" t="inlineStr"/>
+      <c r="Q290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr"/>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Mahidol University</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" t="inlineStr"/>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr"/>
+      <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr"/>
+      <c r="J291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>http://www.mahidol.ac.th/en/</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr"/>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr"/>
+      <c r="P291" t="inlineStr"/>
+      <c r="Q291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr"/>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Southwest Jiaotong University</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" t="inlineStr"/>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr"/>
+      <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr"/>
+      <c r="J292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>https://swjtu.edu.cn</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr"/>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr"/>
+      <c r="P292" t="inlineStr"/>
+      <c r="Q292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr"/>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>RMIT University</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr"/>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr"/>
+      <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr"/>
+      <c r="J293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>https://www.rmit.edu.au/</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr"/>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr"/>
+      <c r="P293" t="inlineStr"/>
+      <c r="Q293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr"/>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>East China Normal University</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="inlineStr"/>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr"/>
+      <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr"/>
+      <c r="J294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>https://www.ecnu.edu.cn</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr"/>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr"/>
+      <c r="P294" t="inlineStr"/>
+      <c r="Q294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr"/>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Chulalongkorn University</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="inlineStr"/>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr"/>
+      <c r="H295" t="inlineStr"/>
+      <c r="I295" t="inlineStr"/>
+      <c r="J295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>https://www.chula.ac.th/</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr"/>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr"/>
+      <c r="P295" t="inlineStr"/>
+      <c r="Q295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr"/>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>University of Newcastle Australia</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="inlineStr"/>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr"/>
+      <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr"/>
+      <c r="J296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>https://www.newcastle.edu.au</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr"/>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr"/>
+      <c r="P296" t="inlineStr"/>
+      <c r="Q296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr"/>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Martin Luther University Halle-Wittenberg</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="inlineStr"/>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr"/>
+      <c r="H297" t="inlineStr"/>
+      <c r="I297" t="inlineStr"/>
+      <c r="J297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>https://www.uni-halle.de/</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr"/>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr"/>
+      <c r="P297" t="inlineStr"/>
+      <c r="Q297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr"/>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>La Trobe University</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="inlineStr"/>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr"/>
+      <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr"/>
+      <c r="J298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>http://www.latrobe.edu.au/</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr"/>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr"/>
+      <c r="P298" t="inlineStr"/>
+      <c r="Q298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr"/>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Hacettepe University</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Türkiye</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr"/>
+      <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr"/>
+      <c r="J299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>https://www.hacettepe.edu.tr</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr"/>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr"/>
+      <c r="P299" t="inlineStr"/>
+      <c r="Q299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr"/>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>University of Wollongong</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr"/>
+      <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr"/>
+      <c r="J300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>https://www.uow.edu.au</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr"/>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr"/>
+      <c r="P300" t="inlineStr"/>
+      <c r="Q300" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -11309,23 +11309,35 @@
       <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
-          <t>http://english.hust.edu.cn/</t>
+          <t>https://openalex.org/A5102780663</t>
         </is>
       </c>
       <c r="L201" t="inlineStr"/>
       <c r="M201" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O201" t="inlineStr"/>
-      <c r="P201" t="inlineStr"/>
-      <c r="Q201" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>FPGA &amp; Edge AI</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>Zhe Jiang</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>MERE: Hardware-Software Co-Design for Masking Cache Miss Latency in Embedded Processors (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr"/>
@@ -11348,23 +11360,35 @@
       <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
-          <t>https://ustc.edu.cn</t>
+          <t>https://openalex.org/A5100678341</t>
         </is>
       </c>
       <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O202" t="inlineStr"/>
-      <c r="P202" t="inlineStr"/>
-      <c r="Q202" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>Tao Jiang</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>AutoLoc: Toward Ubiquitous AoA-Based Indoor Localization Using Commodity WiFi (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr"/>
@@ -11387,23 +11411,35 @@
       <c r="J203" t="inlineStr"/>
       <c r="K203" t="inlineStr">
         <is>
-          <t>https://www.uestc.edu.cn</t>
+          <t>https://openalex.org/A5101989539</t>
         </is>
       </c>
       <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O203" t="inlineStr"/>
-      <c r="P203" t="inlineStr"/>
-      <c r="Q203" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>Gang Feng</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>An Adapted Mean Teacher Model for Semi-supervised Indoor Positioning using Channel Impulse Response (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr"/>
@@ -11424,25 +11460,33 @@
       <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>https://www.qmul.ac.uk/</t>
-        </is>
-      </c>
+      <c r="K204" t="inlineStr"/>
       <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O204" t="inlineStr"/>
-      <c r="P204" t="inlineStr"/>
-      <c r="Q204" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>Arumugam Nallanathan</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>Multi-waveguide indoor positioning for PASS (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr"/>
@@ -11465,23 +11509,35 @@
       <c r="J205" t="inlineStr"/>
       <c r="K205" t="inlineStr">
         <is>
-          <t>https://tu-dresden.de</t>
+          <t>https://openalex.org/A5118360762</t>
         </is>
       </c>
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O205" t="inlineStr"/>
-      <c r="P205" t="inlineStr"/>
-      <c r="Q205" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>Muhammad Ammad</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>From Least Squares to Deep Learning: Benchmarking Indoor Positioning on the HYMN Multi-Technology Dataset (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr"/>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -11560,23 +11560,35 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
-          <t>https://bit.edu.cn</t>
+          <t>https://openalex.org/A5064231378</t>
         </is>
       </c>
       <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O206" t="inlineStr"/>
-      <c r="P206" t="inlineStr"/>
-      <c r="Q206" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>Yuanqing Xia</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>Indoor Positioning Systems Based on a Modified Matrix-Weighted Fusion Estimator With Multipath and NLOS Mitigation (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr"/>
@@ -11599,23 +11611,35 @@
       <c r="J207" t="inlineStr"/>
       <c r="K207" t="inlineStr">
         <is>
-          <t>https://www.nwpu.edu.cn</t>
+          <t>https://openalex.org/A5013368501</t>
         </is>
       </c>
       <c r="L207" t="inlineStr"/>
       <c r="M207" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O207" t="inlineStr"/>
-      <c r="P207" t="inlineStr"/>
-      <c r="Q207" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>Rugui Yao</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>Research on Key Technologies of Indoor High-Precision Positioning Based on UWB (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr"/>
@@ -11638,23 +11662,35 @@
       <c r="J208" t="inlineStr"/>
       <c r="K208" t="inlineStr">
         <is>
-          <t>https://uclouvain.be</t>
+          <t>https://openalex.org/A5040643249</t>
         </is>
       </c>
       <c r="L208" t="inlineStr"/>
       <c r="M208" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O208" t="inlineStr"/>
-      <c r="P208" t="inlineStr"/>
-      <c r="Q208" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>Isabelle Huynen</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>Sub-terahertz absorption shielding performances of polyurethane - Carbon nanotubes composite foams (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr"/>
@@ -11677,23 +11713,35 @@
       <c r="J209" t="inlineStr"/>
       <c r="K209" t="inlineStr">
         <is>
-          <t>https://www.auckland.ac.nz/en.html</t>
+          <t>https://openalex.org/A5077911956</t>
         </is>
       </c>
       <c r="L209" t="inlineStr"/>
       <c r="M209" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O209" t="inlineStr"/>
-      <c r="P209" t="inlineStr"/>
-      <c r="Q209" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>Zhishu Zhang</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>Augmented reality and indoor positioning based mobile production monitoring system to support workers with human-in-the-loop (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr"/>
@@ -11716,23 +11764,35 @@
       <c r="J210" t="inlineStr"/>
       <c r="K210" t="inlineStr">
         <is>
-          <t>https://www.cqu.edu.cn</t>
+          <t>https://openalex.org/A5009166877</t>
         </is>
       </c>
       <c r="L210" t="inlineStr"/>
       <c r="M210" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O210" t="inlineStr"/>
-      <c r="P210" t="inlineStr"/>
-      <c r="Q210" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>Jiangshuai Huang</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>Tightly Coupled UWB/VIO Indoor Localization via Robust Ranging and Anisotropic Fusion (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr"/>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -11815,23 +11815,35 @@
       <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
-          <t>https://www.dlut.edu.cn</t>
+          <t>https://openalex.org/A5101887510</t>
         </is>
       </c>
       <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O211" t="inlineStr"/>
-      <c r="P211" t="inlineStr"/>
-      <c r="Q211" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>Xin Chao Zhao</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>Research on indoor positioning method based on improved UKF multisensor fusion (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr"/>
@@ -11854,23 +11866,35 @@
       <c r="J212" t="inlineStr"/>
       <c r="K212" t="inlineStr">
         <is>
-          <t>https://www.zzu.edu.cn</t>
+          <t>https://openalex.org/A5046094598</t>
         </is>
       </c>
       <c r="L212" t="inlineStr"/>
       <c r="M212" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O212" t="inlineStr"/>
-      <c r="P212" t="inlineStr"/>
-      <c r="Q212" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>Yingqiang Ding</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>UWB indoor localization method based on neural network multi-classification for NLOS distance correction (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr"/>
@@ -11893,23 +11917,35 @@
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
-          <t>https://www.ruhr-uni-bochum.de</t>
+          <t>https://openalex.org/A5071644998</t>
         </is>
       </c>
       <c r="L213" t="inlineStr"/>
       <c r="M213" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O213" t="inlineStr"/>
-      <c r="P213" t="inlineStr"/>
-      <c r="Q213" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>Thomas Kaiser</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>Millimeter Wave Indoor SAR Sensing Assisted With Chipless Tags-Based Self-Localization System: Experimental Evaluation (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr"/>
@@ -11932,23 +11968,35 @@
       <c r="J214" t="inlineStr"/>
       <c r="K214" t="inlineStr">
         <is>
-          <t>https://www.uni-jena.de/en</t>
+          <t>https://openalex.org/A5012837694</t>
         </is>
       </c>
       <c r="L214" t="inlineStr"/>
       <c r="M214" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O214" t="inlineStr"/>
-      <c r="P214" t="inlineStr"/>
-      <c r="Q214" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>M. R. C. Mahdy</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>Sierpinski-fractal inspired ultra-broadband UV-NIR meta absorber: Notable impact on the self-stabilization of light-sail or solar-sail (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr"/>
@@ -11971,23 +12019,35 @@
       <c r="J215" t="inlineStr"/>
       <c r="K215" t="inlineStr">
         <is>
-          <t>http://www.hiroshima-u.ac.jp/index.html</t>
+          <t>https://openalex.org/A5091359587</t>
         </is>
       </c>
       <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O215" t="inlineStr"/>
-      <c r="P215" t="inlineStr"/>
-      <c r="Q215" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>Игорь Андреевич Гончаренко</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>Indoor Positioning Using Smartphone Sensors: A LIDAR and IMU-Based Approach (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr"/>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -12070,23 +12070,35 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>http://www.bg.ac.rs/en/</t>
+          <t>https://openalex.org/A5103103788</t>
         </is>
       </c>
       <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O216" t="inlineStr"/>
-      <c r="P216" t="inlineStr"/>
-      <c r="Q216" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>Milan Bjelica</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>Distance Metric Robustness in RSSI Fingerprinting Under Sparse Access Point Conditions (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr"/>
@@ -12109,23 +12121,35 @@
       <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr">
         <is>
-          <t>https://www.univ-lyon1.fr</t>
+          <t>https://openalex.org/A5035953975</t>
         </is>
       </c>
       <c r="L217" t="inlineStr"/>
       <c r="M217" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O217" t="inlineStr"/>
-      <c r="P217" t="inlineStr"/>
-      <c r="Q217" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>Abdesslam Redjaline</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>Indoor positioning systems provide insight into emergency department systems enabling proposal of designs to improve workflow (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr"/>
@@ -12148,23 +12172,35 @@
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
-          <t>http://en.ufsc.br/</t>
+          <t>https://openalex.org/A5067391848</t>
         </is>
       </c>
       <c r="L218" t="inlineStr"/>
       <c r="M218" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O218" t="inlineStr"/>
-      <c r="P218" t="inlineStr"/>
-      <c r="Q218" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>Richard Demo Souza</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>AoA and RSSI-Based BLE Indoor Positioning System With Kalman Filter and Data Fusion (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr"/>
@@ -12187,23 +12223,35 @@
       <c r="J219" t="inlineStr"/>
       <c r="K219" t="inlineStr">
         <is>
-          <t>https://www.xmu.edu.cn</t>
+          <t>https://openalex.org/A5101948255</t>
         </is>
       </c>
       <c r="L219" t="inlineStr"/>
       <c r="M219" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O219" t="inlineStr"/>
-      <c r="P219" t="inlineStr"/>
-      <c r="Q219" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>Jianping Zeng</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>An Indoor Localization Algorithm Using Improved ESKF to Fuse Data from UWB, IMU, and Barometer (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr"/>
@@ -12226,23 +12274,35 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>http://www.technion.ac.il/</t>
+          <t>https://openalex.org/A5068386123</t>
         </is>
       </c>
       <c r="L220" t="inlineStr"/>
       <c r="M220" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O220" t="inlineStr"/>
-      <c r="P220" t="inlineStr"/>
-      <c r="Q220" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>Manish L. Bhaiyya</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>Advancing indoor positioning systems: innovations, challenges, and applications in mobile robotics (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr"/>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -12325,23 +12325,35 @@
       <c r="J221" t="inlineStr"/>
       <c r="K221" t="inlineStr">
         <is>
-          <t>https://www.queensu.ca/</t>
+          <t>https://openalex.org/A5013334648</t>
         </is>
       </c>
       <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O221" t="inlineStr"/>
-      <c r="P221" t="inlineStr"/>
-      <c r="Q221" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>Loay Sabry Ismail</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>Obstacle-Aware Human Localization via Channel Impulse Response (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr"/>
@@ -12364,23 +12376,35 @@
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
-          <t>http://www.unizg.hr/</t>
+          <t>https://openalex.org/A5088884299</t>
         </is>
       </c>
       <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O222" t="inlineStr"/>
-      <c r="P222" t="inlineStr"/>
-      <c r="Q222" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>Niko Jelušić</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>Ultra-wideband Localization with Time-based Measurement Techniques (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr"/>
@@ -12403,23 +12427,35 @@
       <c r="J223" t="inlineStr"/>
       <c r="K223" t="inlineStr">
         <is>
-          <t>https://umanitoba.ca</t>
+          <t>https://openalex.org/A5059955804</t>
         </is>
       </c>
       <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O223" t="inlineStr"/>
-      <c r="P223" t="inlineStr"/>
-      <c r="Q223" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>Αλεξάνδρα Παπαϊωάννου</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>The reliability and validity of a non-wearable indoor positioning system to assess mobility in older adults: A cross-sectional study (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr"/>
@@ -12442,23 +12478,35 @@
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
-          <t>https://www.kaist.ac.kr</t>
+          <t>https://openalex.org/A5017736224</t>
         </is>
       </c>
       <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O224" t="inlineStr"/>
-      <c r="P224" t="inlineStr"/>
-      <c r="Q224" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>Osvaldo Simeone</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>Reliable Wireless Indoor Localization via Cross-Validated Prediction-Powered Calibration (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr"/>
@@ -12479,25 +12527,33 @@
       <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>https://www.cug.edu.cn/</t>
-        </is>
-      </c>
+      <c r="K225" t="inlineStr"/>
       <c r="L225" t="inlineStr"/>
       <c r="M225" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O225" t="inlineStr"/>
-      <c r="P225" t="inlineStr"/>
-      <c r="Q225" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>Zhe Jian</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>WaveletLoc: A Lightweight Deep Learning Model for Indoor Positioning Based on Wavelet Transform (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr"/>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -12576,23 +12576,35 @@
       <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
-          <t>https://www.tuwien.at</t>
+          <t>https://openalex.org/A5089919338</t>
         </is>
       </c>
       <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O226" t="inlineStr"/>
-      <c r="P226" t="inlineStr"/>
-      <c r="Q226" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>Wolfgang Kästner</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>Authenticated UWB-Based Positioning of Passive Drones (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr"/>
@@ -12615,23 +12627,35 @@
       <c r="J227" t="inlineStr"/>
       <c r="K227" t="inlineStr">
         <is>
-          <t>https://www.us.es/</t>
+          <t>https://openalex.org/A5035808386</t>
         </is>
       </c>
       <c r="L227" t="inlineStr"/>
       <c r="M227" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O227" t="inlineStr"/>
-      <c r="P227" t="inlineStr"/>
-      <c r="Q227" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>Javier Medina-Quero</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>Discovering Social Interactions Between Caregivers and Frail Individuals Using Indoor Localization (2024)</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr"/>
@@ -12654,23 +12678,35 @@
       <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>https://www.qub.ac.uk</t>
+          <t>https://openalex.org/A5053763715</t>
         </is>
       </c>
       <c r="L228" t="inlineStr"/>
       <c r="M228" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O228" t="inlineStr"/>
-      <c r="P228" t="inlineStr"/>
-      <c r="Q228" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>Okan Yurduseven</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>Adversarial Learning-Based Radio Map Reconstruction for Fingerprinting Localization (2026)</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr"/>
@@ -12693,23 +12729,35 @@
       <c r="J229" t="inlineStr"/>
       <c r="K229" t="inlineStr">
         <is>
-          <t>https://nankai.edu.cn</t>
+          <t>https://openalex.org/A5101939770</t>
         </is>
       </c>
       <c r="L229" t="inlineStr"/>
       <c r="M229" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O229" t="inlineStr"/>
-      <c r="P229" t="inlineStr"/>
-      <c r="Q229" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>Hong Wu</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>Fingerprint Fusion Location Method Based on Wireless Signal Distribution Characteristic (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr"/>
@@ -12732,23 +12780,35 @@
       <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>https://www.suda.edu.cn</t>
+          <t>https://openalex.org/A5052184480</t>
         </is>
       </c>
       <c r="L230" t="inlineStr"/>
       <c r="M230" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O230" t="inlineStr"/>
-      <c r="P230" t="inlineStr"/>
-      <c r="Q230" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>Weiwei Zhao</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>Laser Vision for Low-Coupling Indoor Positioning (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr"/>

--- a/List of emails.xlsx
+++ b/List of emails.xlsx
@@ -12831,23 +12831,35 @@
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
-          <t>https://www.auth.gr</t>
+          <t>https://openalex.org/A5036495543</t>
         </is>
       </c>
       <c r="L231" t="inlineStr"/>
       <c r="M231" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O231" t="inlineStr"/>
-      <c r="P231" t="inlineStr"/>
-      <c r="Q231" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>Theodore Laopoulos</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>Indoor Positioning System Evaluation in Public Rooms (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr"/>
@@ -12870,23 +12882,35 @@
       <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
-          <t>https://www.dal.ca</t>
+          <t>https://openalex.org/A5077233181</t>
         </is>
       </c>
       <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O232" t="inlineStr"/>
-      <c r="P232" t="inlineStr"/>
-      <c r="Q232" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Jean‐François Bousquet</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>Demonstration of Underwater Channel State Information Acquisition in Grand Passage, Nova Scotia (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr"/>
@@ -12909,23 +12933,35 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>https://www.um.edu.my/</t>
+          <t>https://openalex.org/A5090331621</t>
         </is>
       </c>
       <c r="L233" t="inlineStr"/>
       <c r="M233" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O233" t="inlineStr"/>
-      <c r="P233" t="inlineStr"/>
-      <c r="Q233" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>Jeevan Kanesan</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>Location Accuracy Optimization in Bluetooth Low Energy (BLE) 5.1-Based Indoor Positioning System (IPS)—A Machine Learning Approach (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr"/>
@@ -12948,23 +12984,35 @@
       <c r="J234" t="inlineStr"/>
       <c r="K234" t="inlineStr">
         <is>
-          <t>http://www.univ-paris-diderot.fr/sc/site.php?bc=accueil&amp;np=accueil</t>
+          <t>https://openalex.org/A5001451316</t>
         </is>
       </c>
       <c r="L234" t="inlineStr"/>
       <c r="M234" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O234" t="inlineStr"/>
-      <c r="P234" t="inlineStr"/>
-      <c r="Q234" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>Patrick Mounaix</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>La perception numérique - Projet ciblé COMPTERA: COMPosants électroniques pour l’imagerie TERAhertz (2023)</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr"/>
@@ -12987,23 +13035,35 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>https://www.ufpe.br</t>
+          <t>https://openalex.org/A5029604814</t>
         </is>
       </c>
       <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="O235" t="inlineStr"/>
-      <c r="P235" t="inlineStr"/>
-      <c r="Q235" t="inlineStr"/>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>Localization</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>Ulysses R. C. Vitor</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>A Multiband Yagi-Uda Patch Antenna with Different Orders of Koch Fractal (2025)</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr"/>
